--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.731665864549995</v>
+        <v>1.256395702989374</v>
       </c>
       <c r="D2" t="n">
-        <v>6.44885692820855</v>
+        <v>1.047939250833889</v>
       </c>
       <c r="E2" t="n">
-        <v>3.545493320079524</v>
+        <v>0.5761426645129226</v>
       </c>
       <c r="F2" t="n">
-        <v>4.17253674436795</v>
+        <v>0.6780372209597918</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.41408996191057</v>
+        <v>2.667289618810467</v>
       </c>
       <c r="D3" t="n">
-        <v>16.64809723627017</v>
+        <v>2.705315800893903</v>
       </c>
       <c r="E3" t="n">
-        <v>3.545493320079524</v>
+        <v>0.5761426645129226</v>
       </c>
       <c r="F3" t="n">
-        <v>4.17253674436795</v>
+        <v>0.6780372209597918</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.90262275924744</v>
+        <v>1.934176198377709</v>
       </c>
       <c r="D4" t="n">
-        <v>12.12023387298292</v>
+        <v>1.969538004359724</v>
       </c>
       <c r="E4" t="n">
-        <v>3.545493320079524</v>
+        <v>0.5761426645129226</v>
       </c>
       <c r="F4" t="n">
-        <v>4.17253674436795</v>
+        <v>0.6780372209597918</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
